--- a/archive/2026-05-03/2239.xlsx
+++ b/archive/2026-05-03/2239.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.114\Data\3 HOURLY\2026\5-May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB61DCB-50EA-4DAF-83E8-98B76DC737ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED4310D8-F234-4CE0-86F5-008FA7D43E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="601" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="601" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$7:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$11:$K$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Station_ID</t>
   </si>
@@ -188,46 +188,34 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>2026-05-02 1730</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>2026-05-02 2030</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>2026-05-03 0230</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>24.4</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
-    <t>thunderstormsnight</t>
+    <t>Trace</t>
+  </si>
+  <si>
+    <t>2026-05-03 1730</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>2026-05-03 2030</t>
+  </si>
+  <si>
+    <t>2026-05-04 0230</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>26.2</t>
+  </si>
+  <si>
+    <t>2.4</t>
   </si>
 </sst>
 </file>
@@ -803,7 +791,7 @@
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -832,15 +820,15 @@
       <c r="J1" s="30"/>
       <c r="K1" s="30"/>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>43413</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>43404</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>51</v>
@@ -848,25 +836,25 @@
       <c r="E2" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="33">
-        <v>29.1</v>
+      <c r="F2" s="33" t="s">
+        <v>55</v>
       </c>
       <c r="G2" s="3">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>43418</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
+      <c r="A3" s="3">
+        <v>43410</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>51</v>
@@ -875,24 +863,24 @@
         <v>51</v>
       </c>
       <c r="F3" s="33">
-        <v>27.6</v>
+        <v>32.5</v>
       </c>
       <c r="G3" s="3">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>43421</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>43415</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>51</v>
@@ -901,24 +889,25 @@
         <v>51</v>
       </c>
       <c r="F4" s="33">
-        <v>27.5</v>
+        <v>28.8</v>
       </c>
       <c r="G4" s="3">
-        <v>90</v>
-      </c>
-      <c r="H4" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>43424</v>
+        <v>43422</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D5" s="33" t="s">
         <v>51</v>
@@ -927,24 +916,24 @@
         <v>51</v>
       </c>
       <c r="F5" s="33">
-        <v>29.4</v>
+        <v>30.4</v>
       </c>
       <c r="G5" s="3">
-        <v>85</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>43436</v>
+        <v>43413</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="33" t="s">
         <v>51</v>
@@ -953,24 +942,24 @@
         <v>51</v>
       </c>
       <c r="F6" s="33">
-        <v>27.5</v>
+        <v>30.4</v>
       </c>
       <c r="G6" s="3">
-        <v>82</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>38</v>
+        <v>84</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>43441</v>
+        <v>43418</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>51</v>
@@ -978,25 +967,25 @@
       <c r="E7" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>57</v>
+      <c r="F7" s="33">
+        <v>27.6</v>
       </c>
       <c r="G7" s="3">
-        <v>88</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>36</v>
+        <v>87</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>43444</v>
+        <v>43421</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>51</v>
@@ -1005,285 +994,284 @@
         <v>51</v>
       </c>
       <c r="F8" s="33">
-        <v>23.8</v>
+        <v>27.2</v>
       </c>
       <c r="G8" s="3">
-        <v>95</v>
-      </c>
-      <c r="H8" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>43450</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>43424</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="33">
-        <v>3.8</v>
+        <v>52</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>52</v>
       </c>
       <c r="F9" s="33">
-        <v>26.1</v>
+        <v>28.1</v>
       </c>
       <c r="G9" s="3">
-        <v>95</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>42</v>
+        <v>89</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>43466</v>
+        <v>43436</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F10" s="33">
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="G10" s="3">
-        <v>96</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>43467</v>
+        <v>43441</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="33">
-        <v>13.5</v>
+        <v>51</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>51</v>
       </c>
       <c r="F11" s="33">
-        <v>25.7</v>
+        <v>27.2</v>
       </c>
       <c r="G11" s="3">
-        <v>93</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>43473</v>
+        <v>43444</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="33">
-        <v>0.2</v>
+      <c r="E12" s="33" t="s">
+        <v>51</v>
       </c>
       <c r="F12" s="33">
-        <v>13.9</v>
+        <v>23.7</v>
       </c>
       <c r="G12" s="3">
-        <v>95</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>36</v>
+        <v>94</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>43486</v>
+        <v>43450</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="33">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="33">
+        <v>26.7</v>
       </c>
       <c r="G13" s="3">
-        <v>98</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>65</v>
+        <v>92</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>43495</v>
+        <v>43466</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E14" s="33">
-        <v>24.1</v>
+        <v>0.6</v>
       </c>
       <c r="F14" s="33">
-        <v>25.5</v>
+        <v>27.9</v>
       </c>
       <c r="G14" s="3">
-        <v>91</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>41</v>
+        <v>82</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>43497</v>
+        <v>43467</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>51</v>
-      </c>
       <c r="E15" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="33">
+        <v>26.8</v>
+      </c>
+      <c r="G15" s="3">
+        <v>89</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>43473</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="3">
-        <v>85</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>330601</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="D16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="33">
-        <v>0.2</v>
+      <c r="E16" s="33" t="s">
+        <v>52</v>
       </c>
       <c r="F16" s="33">
-        <v>25.8</v>
+        <v>12.4</v>
       </c>
       <c r="G16" s="3">
         <v>92</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>43410</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
+      <c r="A17" s="1">
+        <v>43486</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="33">
-        <v>0.6</v>
-      </c>
-      <c r="F17" s="33">
-        <v>29.5</v>
+        <v>61</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>60</v>
       </c>
       <c r="G17" s="3">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>43415</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>43495</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>51</v>
-      </c>
       <c r="F18" s="33">
-        <v>29.4</v>
+        <v>28.4</v>
       </c>
       <c r="G18" s="3">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="30"/>
+        <v>41</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>43479</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>43497</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>51</v>
@@ -1292,25 +1280,24 @@
         <v>51</v>
       </c>
       <c r="F19" s="33">
-        <v>25.4</v>
+        <v>27.7</v>
       </c>
       <c r="G19" s="3">
-        <v>81</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="30"/>
+        <v>91</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>821501</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>330601</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D20" s="33" t="s">
         <v>51</v>
@@ -1318,14 +1305,14 @@
       <c r="E20" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="33" t="s">
-        <v>54</v>
+      <c r="F20" s="33">
+        <v>26.5</v>
       </c>
       <c r="G20" s="3">
-        <v>72</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>35</v>
+        <v>96</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1336,7 +1323,7 @@
         <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="33" t="s">
         <v>51</v>
@@ -1345,25 +1332,25 @@
         <v>51</v>
       </c>
       <c r="F21" s="33">
-        <v>32.4</v>
+        <v>33.6</v>
       </c>
       <c r="G21" s="3">
-        <v>63</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>34</v>
+        <v>62</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="I21" s="30"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>43404</v>
+        <v>821501</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" s="33" t="s">
         <v>51</v>
@@ -1372,24 +1359,24 @@
         <v>51</v>
       </c>
       <c r="F22" s="33">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="G22" s="3">
-        <v>79</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>43422</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>43475</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>51</v>
@@ -1398,13 +1385,13 @@
         <v>51</v>
       </c>
       <c r="F23" s="33">
-        <v>28.3</v>
+        <v>31.4</v>
       </c>
       <c r="G23" s="3">
-        <v>84</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>38</v>
+        <v>67</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1415,34 +1402,34 @@
         <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E24" s="33">
-        <v>41.2</v>
-      </c>
-      <c r="F24" s="33" t="s">
+        <v>16.7</v>
+      </c>
+      <c r="F24" s="33">
+        <v>19.5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>95</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>43479</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="3">
-        <v>98</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>43475</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="D25" s="33" t="s">
         <v>51</v>
       </c>
@@ -1450,18 +1437,19 @@
         <v>51</v>
       </c>
       <c r="F25" s="33">
-        <v>29.7</v>
+        <v>22.8</v>
       </c>
       <c r="G25" s="3">
-        <v>83</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>38</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="30"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:K21">
-    <sortCondition descending="1" ref="C1:C21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K22">
+    <sortCondition ref="A2:A22"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
@@ -1554,11 +1542,11 @@
         <v>8</v>
       </c>
       <c r="C3" s="32">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D3" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>fairnight</v>
+        <v>cloudy</v>
       </c>
       <c r="E3" s="7">
         <v>3</v>
@@ -1610,11 +1598,11 @@
         <v>10</v>
       </c>
       <c r="C5" s="32">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>fairnight</v>
+        <v>showers</v>
       </c>
       <c r="E5" s="7">
         <v>5</v>
@@ -1638,11 +1626,11 @@
         <v>11</v>
       </c>
       <c r="C6" s="32">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>fairnight</v>
+        <v>partlycloudynight</v>
       </c>
       <c r="E6" s="7">
         <v>6</v>
@@ -1666,11 +1654,11 @@
         <v>12</v>
       </c>
       <c r="C7" s="32">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>fairnight</v>
+        <v>partlycloudynight</v>
       </c>
       <c r="E7" s="7">
         <v>7</v>
@@ -1722,11 +1710,11 @@
         <v>14</v>
       </c>
       <c r="C9" s="32">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D9" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>lightning</v>
+        <v>partlycloudynight</v>
       </c>
       <c r="E9" s="7">
         <v>9</v>
@@ -1750,11 +1738,11 @@
         <v>15</v>
       </c>
       <c r="C10" s="32">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D10" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>thundershowers</v>
+        <v>partlycloudynight</v>
       </c>
       <c r="E10" s="7">
         <v>10</v>
@@ -1778,11 +1766,11 @@
         <v>16</v>
       </c>
       <c r="C11" s="32">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D11" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>thundershowers</v>
+        <v>drizzling</v>
       </c>
       <c r="E11" s="7">
         <v>11</v>
@@ -1834,11 +1822,11 @@
         <v>17</v>
       </c>
       <c r="C13" s="32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>thundershowers</v>
+        <v>showers</v>
       </c>
       <c r="E13" s="7">
         <v>13</v>
@@ -1862,11 +1850,11 @@
         <v>18</v>
       </c>
       <c r="C14" s="32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D14" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>thunderstorms</v>
+        <v>thundershowers</v>
       </c>
       <c r="E14" s="7">
         <v>14</v>
@@ -1890,11 +1878,11 @@
         <v>19</v>
       </c>
       <c r="C15" s="32">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>fairnight</v>
+        <v>partlycloudynight</v>
       </c>
       <c r="E15" s="7">
         <v>15</v>
@@ -1945,10 +1933,12 @@
       <c r="B17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="11" t="e">
+      <c r="C17" s="32">
+        <v>7</v>
+      </c>
+      <c r="D17" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>mist</v>
       </c>
       <c r="E17" s="7">
         <v>17</v>
@@ -1971,10 +1961,12 @@
       <c r="B18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="11" t="e">
+      <c r="C18" s="32">
+        <v>5</v>
+      </c>
+      <c r="D18" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>cloudy</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1984,10 +1976,12 @@
       <c r="B19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="13" t="e">
+      <c r="C19" s="32">
+        <v>10</v>
+      </c>
+      <c r="D19" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>thunderstorms</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1997,10 +1991,12 @@
       <c r="B20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="13" t="e">
+      <c r="C20" s="32">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>drizzling</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -2010,10 +2006,12 @@
       <c r="B21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="13" t="e">
+      <c r="C21" s="32">
+        <v>6</v>
+      </c>
+      <c r="D21" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>partlycloudy</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2023,10 +2021,12 @@
       <c r="B22" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="13" t="e">
+      <c r="C22" s="32">
+        <v>6</v>
+      </c>
+      <c r="D22" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>partlycloudy</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -2036,10 +2036,12 @@
       <c r="B23" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="13" t="e">
+      <c r="C23" s="32">
+        <v>5</v>
+      </c>
+      <c r="D23" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>cloudy</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2049,10 +2051,12 @@
       <c r="B24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="11" t="e">
+      <c r="C24" s="32">
+        <v>5</v>
+      </c>
+      <c r="D24" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>cloudy</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,10 +2066,12 @@
       <c r="B25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="11" t="e">
+      <c r="C25" s="32">
+        <v>5</v>
+      </c>
+      <c r="D25" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
+        <v>cloudy</v>
       </c>
     </row>
   </sheetData>
